--- a/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0013E5FE-1582-4CFE-B87B-92DF023B0D68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0497446B-237B-4903-8D25-937941F7935F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F05AA592-FBF2-4B23-9DC6-A1D19291EF42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21567508-5D38-44F4-9B52-322A5C817B8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{927752B0-C4F4-4CA3-B432-96228AEF809B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4035EC2C-58D7-4399-9D77-E3FD516D3660}"/>
 </file>